--- a/02_Output/G-Form/Summary_results/heatmap_rd_min_max_by_scenario.xlsx
+++ b/02_Output/G-Form/Summary_results/heatmap_rd_min_max_by_scenario.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -370,96 +370,338 @@
           <t>max_risk_difference</t>
         </is>
       </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>min_risk_difference_pp</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>max_risk_difference_pp</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>pm25_pct20</t>
+          <t>pm25_pct10</t>
         </is>
       </c>
       <c r="B2">
-        <v>-0.000211402480674888</v>
+        <v>-0.000105918817749198</v>
       </c>
       <c r="C2">
-        <v>8.017210075887681E-05</v>
+        <v>4.00517331022865E-05</v>
+      </c>
+      <c r="D2">
+        <v>-0.0105918817749198</v>
+      </c>
+      <c r="E2">
+        <v>0.00400517331022865</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>no2_pct20</t>
+          <t>no2_pct10</t>
         </is>
       </c>
       <c r="B3">
-        <v>-0.000191534074915234</v>
+        <v>-9.609776307351051E-05</v>
       </c>
       <c r="C3">
-        <v>0.000123412405275539</v>
+        <v>6.15472515520521E-05</v>
+      </c>
+      <c r="D3">
+        <v>-0.009609776307351051</v>
+      </c>
+      <c r="E3">
+        <v>0.00615472515520521</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>o3_pct20</t>
+          <t>o3_pct10</t>
         </is>
       </c>
       <c r="B4">
-        <v>-0.000446660614438668</v>
+        <v>-0.000224196299434223</v>
       </c>
       <c r="C4">
-        <v>5.15803165786876E-05</v>
+        <v>2.57141211486497E-05</v>
+      </c>
+      <c r="D4">
+        <v>-0.0224196299434223</v>
+      </c>
+      <c r="E4">
+        <v>0.00257141211486497</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>pm25_lt20</t>
+          <t>pm25_pct20</t>
         </is>
       </c>
       <c r="B5">
-        <v>-0.000301376886708962</v>
+        <v>-0.000211402480674888</v>
       </c>
       <c r="C5">
-        <v>0.000115616443165698</v>
+        <v>8.017210075887681E-05</v>
+      </c>
+      <c r="D5">
+        <v>-0.0211402480674888</v>
+      </c>
+      <c r="E5">
+        <v>0.00801721007588768</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>no2_lt20</t>
+          <t>no2_pct20</t>
         </is>
       </c>
       <c r="B6">
-        <v>-0.000178079062045589</v>
+        <v>-0.000191534074915234</v>
       </c>
       <c r="C6">
-        <v>0.000117011912547885</v>
+        <v>0.000123412405275539</v>
+      </c>
+      <c r="D6">
+        <v>-0.0191534074915234</v>
+      </c>
+      <c r="E6">
+        <v>0.0123412405275539</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>pm25_lt5</t>
+          <t>o3_pct20</t>
         </is>
       </c>
       <c r="B7">
-        <v>-0.000839092147527254</v>
+        <v>-0.000446660614438668</v>
       </c>
       <c r="C7">
-        <v>0.000324448997919141</v>
+        <v>5.15803165786876E-05</v>
+      </c>
+      <c r="D7">
+        <v>-0.0446660614438668</v>
+      </c>
+      <c r="E7">
+        <v>0.00515803165786876</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>pm25_pct30</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>-0.000316453017176602</v>
+      </c>
+      <c r="C8">
+        <v>0.000120361192254129</v>
+      </c>
+      <c r="D8">
+        <v>-0.0316453017176602</v>
+      </c>
+      <c r="E8">
+        <v>0.0120361192254129</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>no2_pct30</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>-0.000286313933674107</v>
+      </c>
+      <c r="C9">
+        <v>0.000185595715550504</v>
+      </c>
+      <c r="D9">
+        <v>-0.0286313933674107</v>
+      </c>
+      <c r="E9">
+        <v>0.0185595715550504</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>o3_pct30</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>-0.000667413238342116</v>
+      </c>
+      <c r="C10">
+        <v>7.759956376244929E-05</v>
+      </c>
+      <c r="D10">
+        <v>-0.06674132383421159</v>
+      </c>
+      <c r="E10">
+        <v>0.007759956376244929</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>pm25_lt20</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>-0.000301376886708962</v>
+      </c>
+      <c r="C11">
+        <v>0.000115616443165698</v>
+      </c>
+      <c r="D11">
+        <v>-0.0301376886708962</v>
+      </c>
+      <c r="E11">
+        <v>0.0115616443165698</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>no2_lt20</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>-0.000178079062045589</v>
+      </c>
+      <c r="C12">
+        <v>0.000117011912547885</v>
+      </c>
+      <c r="D12">
+        <v>-0.0178079062045589</v>
+      </c>
+      <c r="E12">
+        <v>0.0117011912547885</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>pm25_lt15</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>-0.000443052550336845</v>
+      </c>
+      <c r="C13">
+        <v>0.000170348206046833</v>
+      </c>
+      <c r="D13">
+        <v>-0.0443052550336845</v>
+      </c>
+      <c r="E13">
+        <v>0.0170348206046833</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>no2_lt15</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>-0.000305124826446859</v>
+      </c>
+      <c r="C14">
+        <v>0.000201710298125921</v>
+      </c>
+      <c r="D14">
+        <v>-0.0305124826446859</v>
+      </c>
+      <c r="E14">
+        <v>0.0201710298125921</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>pm25_lt10</t>
+        </is>
+      </c>
+      <c r="B15">
+        <v>-0.0006370178215565489</v>
+      </c>
+      <c r="C15">
+        <v>0.00024551114398709</v>
+      </c>
+      <c r="D15">
+        <v>-0.06370178215565489</v>
+      </c>
+      <c r="E15">
+        <v>0.024551114398709</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>no2_lt10</t>
+        </is>
+      </c>
+      <c r="B16">
+        <v>-0.000492906571576107</v>
+      </c>
+      <c r="C16">
+        <v>0.000327602129040427</v>
+      </c>
+      <c r="D16">
+        <v>-0.0492906571576107</v>
+      </c>
+      <c r="E16">
+        <v>0.03276021290404271</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>pm25_lt5</t>
+        </is>
+      </c>
+      <c r="B17">
+        <v>-0.000839092147527254</v>
+      </c>
+      <c r="C17">
+        <v>0.000324448997919141</v>
+      </c>
+      <c r="D17">
+        <v>-0.08390921475272541</v>
+      </c>
+      <c r="E17">
+        <v>0.0324448997919141</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>no2_lt5</t>
         </is>
       </c>
-      <c r="B8">
+      <c r="B18">
         <v>-0.00071357655111233</v>
       </c>
-      <c r="C8">
+      <c r="C18">
         <v>0.00047768367604456</v>
+      </c>
+      <c r="D18">
+        <v>-0.071357655111233</v>
+      </c>
+      <c r="E18">
+        <v>0.047768367604456</v>
       </c>
     </row>
   </sheetData>
